--- a/artfynd/A 21748-2024 artfynd.xlsx
+++ b/artfynd/A 21748-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,7 +811,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103030102</v>
+        <v>103030103</v>
       </c>
       <c r="B3" t="n">
         <v>92939</v>
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562072.1851685513</v>
+        <v>561999.8165287246</v>
       </c>
       <c r="R3" t="n">
-        <v>6314267.897362486</v>
+        <v>6314248.826037287</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>D9BBAB23-C2EE-4DFC-AC1F-D6EA1B579672</t>
+          <t>37A88206-4D19-41B1-A616-D6463483F8B6</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -952,10 +952,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103030103</v>
+        <v>103030186</v>
       </c>
       <c r="B4" t="n">
-        <v>92939</v>
+        <v>77706</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -968,21 +968,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2779</v>
+        <v>1639</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1086,147 +1086,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>103030186</v>
-      </c>
-      <c r="B5" t="n">
-        <v>77706</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1639</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Blomskägglav</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Usnea florida</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Kalmar län, Sm</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>561999.8165287246</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6314248.826037287</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Nybro</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Bäckebo</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>37A88206-4D19-41B1-A616-D6463483F8B6</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2015-03-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2015-03-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad i samband med trädinventering.</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Thomas Johansson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Marion Jannes</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>
